--- a/results/Int All Data 0.2/Linea_fi_explain.xlsx
+++ b/results/Int All Data 0.2/Linea_fi_explain.xlsx
@@ -1715,7 +1715,7 @@
         <v>0.003605224323002529</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0008306156791318431</v>
+        <v>0.0008347771439674646</v>
       </c>
       <c r="P3" t="n">
         <v>-0.0006198702243907893</v>
@@ -1829,7 +1829,7 @@
         <v>-9.013478622203474e-05</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.02180893220037367</v>
+        <v>0.02180923178018043</v>
       </c>
       <c r="BB3" t="n">
         <v>0.009858935378542304</v>
@@ -1856,7 +1856,7 @@
         <v>0.161792153723798</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.004807416654150294</v>
+        <v>0.004803255189314673</v>
       </c>
       <c r="BK3" t="n">
         <v>0.02050104892412701</v>
@@ -1868,7 +1868,7 @@
         <v>0.005247620213850107</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.02180536330822685</v>
+        <v>0.02180923178018043</v>
       </c>
       <c r="BO3" t="n">
         <v>0.01276420919561758</v>
@@ -1883,7 +1883,7 @@
         <v>0.01798685025867868</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.005705508406032874</v>
+        <v>0.005705827538769413</v>
       </c>
       <c r="BT3" t="n">
         <v>-0.0004958064998837996</v>
@@ -1892,13 +1892,13 @@
         <v>0.008408666223998558</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.0005681141596791306</v>
+        <v>0.000564070488025269</v>
       </c>
       <c r="BW3" t="n">
         <v>0.0001264987908546167</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.0006100768682952051</v>
+        <v>0.0006020883554048715</v>
       </c>
       <c r="BY3" t="n">
         <v>0.0004829582045663439</v>
@@ -1910,7 +1910,7 @@
         <v>0.002841196617875227</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.02069167582424379</v>
+        <v>0.02068748821955367</v>
       </c>
       <c r="CC3" t="n">
         <v>0.001035925098257751</v>
@@ -1922,7 +1922,7 @@
         <v>-0.0004039456867998791</v>
       </c>
       <c r="CF3" t="n">
-        <v>-0.001125802554734718</v>
+        <v>-0.001121058880493158</v>
       </c>
       <c r="CG3" t="n">
         <v>0.4351824709360194</v>
@@ -1934,7 +1934,7 @@
         <v>0.2670207832827591</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.0001264987908546156</v>
+        <v>0.0001306881498826851</v>
       </c>
       <c r="CK3" t="n">
         <v>0.002091271211970036</v>
@@ -1964,7 +1964,7 @@
         <v>0.3574069608977497</v>
       </c>
       <c r="CT3" t="n">
-        <v>0.0752387369387252</v>
+        <v>0.07524292629775327</v>
       </c>
       <c r="CU3" t="n">
         <v>0.01531799721436316</v>
@@ -2024,7 +2024,7 @@
         <v>0.004704279971210345</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.01033011046395958</v>
+        <v>0.01032611206331984</v>
       </c>
       <c r="DO3" t="n">
         <v>0.006230157453373145</v>
@@ -2054,7 +2054,7 @@
         <v>0.00265757780010389</v>
       </c>
       <c r="DX3" t="n">
-        <v>-0.0003381964668123415</v>
+        <v>-0.000345980365547438</v>
       </c>
       <c r="DY3" t="n">
         <v>0.006259695540170989</v>
@@ -2120,7 +2120,7 @@
         <v>-3.598184847451117e-05</v>
       </c>
       <c r="ET3" t="n">
-        <v>0.001827744002376978</v>
+        <v>0.001831659429158498</v>
       </c>
       <c r="EU3" t="n">
         <v>0.0565904369968516</v>
@@ -2184,7 +2184,7 @@
         <v>0.008721020156629813</v>
       </c>
       <c r="O4" t="n">
-        <v>0.009046401062990848</v>
+        <v>0.009045007543209607</v>
       </c>
       <c r="P4" t="n">
         <v>0.003638412276048989</v>
@@ -2298,7 +2298,7 @@
         <v>0.002921007949844674</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.02424837105842254</v>
+        <v>0.02425770386439996</v>
       </c>
       <c r="BB4" t="n">
         <v>0.01553404136973443</v>
@@ -2325,7 +2325,7 @@
         <v>0.06742346282115426</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.009319466700657151</v>
+        <v>0.009323140585308727</v>
       </c>
       <c r="BK4" t="n">
         <v>0.05018107824671741</v>
@@ -2337,7 +2337,7 @@
         <v>0.01894354752721827</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.02425639608542894</v>
+        <v>0.02425770386439996</v>
       </c>
       <c r="BO4" t="n">
         <v>0.02408703450086898</v>
@@ -2352,7 +2352,7 @@
         <v>0.02622638191785939</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.01064054656855077</v>
+        <v>0.01063927247224608</v>
       </c>
       <c r="BT4" t="n">
         <v>0.002385469631078586</v>
@@ -2361,13 +2361,13 @@
         <v>0.01203785623199518</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.003465430375280468</v>
+        <v>0.003472160635766382</v>
       </c>
       <c r="BW4" t="n">
         <v>0.0004736513178868923</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.005884817105065357</v>
+        <v>0.005921570183670163</v>
       </c>
       <c r="BY4" t="n">
         <v>0.002567320489587855</v>
@@ -2379,7 +2379,7 @@
         <v>0.009156056533704264</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.01990018760544538</v>
+        <v>0.01989538514747079</v>
       </c>
       <c r="CC4" t="n">
         <v>0.007986301065586206</v>
@@ -2391,7 +2391,7 @@
         <v>0.003976928366322996</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.003576532947173374</v>
+        <v>0.003548622683771261</v>
       </c>
       <c r="CG4" t="n">
         <v>0.08878792003635518</v>
@@ -2403,7 +2403,7 @@
         <v>0.07973101342862225</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.0004736513178868912</v>
+        <v>0.0004779263800328203</v>
       </c>
       <c r="CK4" t="n">
         <v>0.006958324691286539</v>
@@ -2433,7 +2433,7 @@
         <v>0.0961452606520375</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.05754853644281031</v>
+        <v>0.05754601697936977</v>
       </c>
       <c r="CU4" t="n">
         <v>0.0219159789479737</v>
@@ -2493,7 +2493,7 @@
         <v>0.02002378614361846</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.01298809520795041</v>
+        <v>0.01298850285324999</v>
       </c>
       <c r="DO4" t="n">
         <v>0.02833101670325045</v>
@@ -2523,7 +2523,7 @@
         <v>0.003971651979010215</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.007327590945160842</v>
+        <v>0.007323829381941556</v>
       </c>
       <c r="DY4" t="n">
         <v>0.02321744464310264</v>
@@ -2589,7 +2589,7 @@
         <v>0.001814521578338792</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.01618649890938685</v>
+        <v>0.01619312497097076</v>
       </c>
       <c r="EU4" t="n">
         <v>0.05949462125565318</v>
@@ -2830,13 +2830,13 @@
         <v>-0.01152446421350589</v>
       </c>
       <c r="BV5" t="n">
-        <v>-0.004609785685402401</v>
+        <v>-0.004650222401941018</v>
       </c>
       <c r="BW5" t="n">
         <v>-0.0005443234836702615</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0.01289931257581889</v>
+        <v>-0.01302062272543474</v>
       </c>
       <c r="BY5" t="n">
         <v>-0.003598560575769727</v>
@@ -2860,7 +2860,7 @@
         <v>-0.01064996084573225</v>
       </c>
       <c r="CF5" t="n">
-        <v>-0.01002830570157703</v>
+        <v>-0.009947432268499801</v>
       </c>
       <c r="CG5" t="n">
         <v>0.3101801096319498</v>
@@ -2992,7 +2992,7 @@
         <v>-0.002505873140172321</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.0119922630560928</v>
+        <v>-0.01203094777562858</v>
       </c>
       <c r="DY5" t="n">
         <v>-0.03222806308127783</v>
@@ -3122,7 +3122,7 @@
         <v>-0.0004715681417089667</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.00140428517557912</v>
+        <v>-0.00137307418931196</v>
       </c>
       <c r="P6" t="n">
         <v>-0.002633984152739924</v>
@@ -3236,7 +3236,7 @@
         <v>-0.001387287093034523</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.008593833986712674</v>
+        <v>0.008584113924504276</v>
       </c>
       <c r="BB6" t="n">
         <v>0.003941067968250911</v>
@@ -3290,7 +3290,7 @@
         <v>0.003990637423092244</v>
       </c>
       <c r="BS6" t="n">
-        <v>0.0008907492279469963</v>
+        <v>0.0009012182396722884</v>
       </c>
       <c r="BT6" t="n">
         <v>-0.001188660096096186</v>
@@ -3371,7 +3371,7 @@
         <v>0.3204626987401749</v>
       </c>
       <c r="CT6" t="n">
-        <v>0.04439198242995458</v>
+        <v>0.04442340262266509</v>
       </c>
       <c r="CU6" t="n">
         <v>0.0008921719109746622</v>
@@ -3744,7 +3744,7 @@
         <v>0.0002297338903559321</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.02532857518210469</v>
+        <v>0.02534791754187258</v>
       </c>
       <c r="BO7" t="n">
         <v>0.01450494736739793</v>
@@ -3759,7 +3759,7 @@
         <v>0.01305583338512104</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.007266666072431377</v>
+        <v>0.007247323712663489</v>
       </c>
       <c r="BT7" t="n">
         <v>-0.0002708935832968329</v>
@@ -4267,7 +4267,7 @@
         <v>0.002132195675975493</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.0001084185833261753</v>
+        <v>0.0001450682651202961</v>
       </c>
       <c r="CG8" t="n">
         <v>0.5011756535329535</v>
@@ -4369,7 +4369,7 @@
         <v>0.002977412894387832</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.01351575621695335</v>
+        <v>0.01350576021535399</v>
       </c>
       <c r="DO8" t="n">
         <v>0.001626256686397828</v>
@@ -4643,7 +4643,7 @@
         <v>0.004327923429047009</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.06796482412060299</v>
+        <v>0.06800670016750418</v>
       </c>
       <c r="BB9" t="n">
         <v>0.03675697533360291</v>
@@ -4712,7 +4712,7 @@
         <v>0.001051354630004031</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.007995028997514553</v>
+        <v>0.008036454018227068</v>
       </c>
       <c r="BY9" t="n">
         <v>0.005324980422866066</v>
@@ -4868,7 +4868,7 @@
         <v>0.009803100125680798</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.01754111198120589</v>
+        <v>0.0175019577133907</v>
       </c>
       <c r="DY9" t="n">
         <v>0.06228239845261124</v>
@@ -4934,7 +4934,7 @@
         <v>0.002545027407987433</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.02646828504306964</v>
+        <v>0.02650743931088484</v>
       </c>
       <c r="EU9" t="n">
         <v>0.1780657640232109</v>
